--- a/data_extactor/batch_10_fa/trimmed/batch_0039_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0039_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | مخابرات و ارتباطات از راه دور | رایانه و الکترونیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | مخابرات | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | درک کتبی | ابتکار و اصالت | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | درک کتبی | اصالت | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | مدیران برنامه‌ریزی و پخش رسانه | رهبران ارکستر، مدیران موسیقی و آهنگسازان | هنرمندان جلوه‌های ویژه و پویانماها</t>
+          <t>بازیگران | مدیران هنری | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | مدیران برنامه‌ریزی و پخش رسانه | رهبران ارکستر، مدیران موسیقی و آهنگسازان | پویانماها و طراحان جلوه‌های ویژه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | شنیدن فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | گوش دادن فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | رایانه و الکترونیک | مدیریت و امور اداری | مخابرات و ارتباطات از راه دور | خدمات مشتریان و خدمات فردی | بازاریابی و فروش</t>
+          <t>ارتباطات و رسانه | رایانه و الکترونیک | مدیریت و اداره | مخابرات | خدمات مشتری و شخصی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | روانی و سیالی ایده‌ها | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | روانی ایده‌ها | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران هنری | گویندگان و مجریان رادیو و تلویزیون | کتابداران و متخصصان مجموعه‌های چندرسانه‌ای | مدیران فنی رسانه | تهیه‌کنندگان و کارگردانان | مدیران روابط عمومی | مسئولان انتخاب بازیگر و استعدادیابی</t>
+          <t>مدیران هنری | گویندگان پخش و مجریان رادیویی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | مدیران فنی رسانه | تهیه‌کنندگان و کارگردانان | مدیران روابط عمومی | مسئولان انتخاب بازیگر و استعدادیابی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | امور کارکنان و منابع انسانی | مدیریت و امور اداری | اداری و دفتری | هنرهای زیبا</t>
+          <t>خدمات مشتری و شخصی | ارتباطات و رسانه | پرسنل و منابع انسانی | مدیریت و اداره | اداری | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | ابتکار و اصالت | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال استقرایی | وضوح گفتار | اصالت | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بازیگران | نمایندگان و مدیران برنامه‌های هنرمندان و ورزشکاران | مدیران هنری | متخصصان منابع انسانی | مدیران برنامه‌ریزی و پخش رسانه | موسیقی‌دانان و خوانندگان | تهیه‌کنندگان و کارگردانان</t>
+          <t>بازیگران | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مدیران هنری | کارشناسان منابع انسانی | مدیران برنامه‌ریزی و پخش رسانه | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مخابرات و ارتباطات از راه دور | فنی و مهندسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>ارتباطات و رسانه | رایانه و الکترونیک | زبان انگلیسی | مخابرات | مهندسی و فناوری | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های صوت و تصویر | تکنسین‌های پخش رادیو و تلویزیون | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | مدیران برنامه‌ریزی و پخش رسانه | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | مدیران برنامه‌ریزی و پخش رسانه | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | امور کارکنان و منابع انسانی | ارتباطات و رسانه | آموزش | بازاریابی و فروش</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | آموزش و پرورش | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>قدرت ایستا | استقامت بدنی | قدرت انفجاری | قدرت پویا | هماهنگی حرکتی کل بدن | هماهنگی چند عضو بدن | انعطاف‌پذیری حرکتی</t>
+          <t>قدرت ایستا | استقامت | قدرت انفجاری | قدرت پویا | هماهنگی کلی بدن | هماهنگی چند عضو | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مربیان و امدادگران ورزشی (اتلتیک ترینرها) | مربیان و استعدادیابان ورزشی | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | هماهنگ‌کنندگان تناسب اندام و سلامت | کارشناسان و مربیان امور تفریحی | پزشکان متخصص پزشکی ورزشی | داوران و مسئولان مسابقات ورزشی</t>
+          <t>مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مربیان و استعدادیابان ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | پزشکان طب ورزشی | داوران و مسئولان مسابقات ورزشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | استراتژی‌های یادگیری | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش | مدیریت و امور اداری | روان‌شناسی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | ایمنی و امنیت عمومی</t>
+          <t>آموزش و پرورش | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | ارتباطات و رسانه | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | ابتکار و اصالت | مرتب‌سازی اطلاعات | درک کتبی | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | اصالت | ترتیب‌دهی اطلاعات | درک کتبی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ورزشکاران و قهرمانان حرفه‌ای | مربیان و امدادگران ورزشی (اتلتیک ترینرها) | مشاوران تحصیلی، راهنمایی و شغلی | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | مدرسان دانشگاهی رشته‌های تربیت بدنی و علوم ورزشی | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی | داوران و مسئولان مسابقات ورزشی</t>
+          <t>ورزشکاران و قهرمانان حرفه‌ای | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مشاوران تحصیلی، شغلی و هدایت استعدادها | مربیان ورزش و آمادگی جسمانی گروهی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | داوران و مسئولان مسابقات ورزشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | نظارت | یادگیری فعال | درک مطلب | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | نظارت | یادگیری فعال | درک مطلب | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید دور | دید نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی</t>
+          <t>بیان شفاهی | بینایی دور | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ورزشکاران و قهرمانان حرفه‌ای | مربیان و امدادگران ورزشی (اتلتیک ترینرها) | مربیان و استعدادیابان ورزشی | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات شرط‌بندی | برنامه‌ریزان همایش‌ها، گردهمایی‌ها و رویدادها | کارشناسان و مربیان امور تفریحی</t>
+          <t>ورزشکاران و قهرمانان حرفه‌ای | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | مربیان و استعدادیابان ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | کارکنان و متصدیان امور تفریحی و اوقات فراغت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>هماهنگی حرکتی کل بدن | انعطاف‌پذیری حرکتی | قدرت پویا | استقامت بدنی | قدرت تنه | تعادل عمومی بدن | هماهنگی چند عضو بدن</t>
+          <t>هماهنگی کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت پویا | استقامت | قدرت تنه | تعادل کلی بدن | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بازیگران | استادان و مدرسان دانشگاهی هنر، تئاتر و موسیقی | طراحان حرکت (کوروگراف‌ها) | مربیان ورزشی و تمرین‌دهندگان آمادگی جسمانی گروهی | چهره‌پردازان و گریمورهای تئاتر و سینما | موسیقی‌دانان و خوانندگان | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی</t>
+          <t>بازیگران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | طراحان حرکت و کوروگراف‌ها | مربیان ورزش و آمادگی جسمانی گروهی | چهره‌پردازان و گریموران تئاتر و سینما | نوازندگان و خوانندگان | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | استراتژی‌های یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | آموزش | مدیریت و امور اداری | تولید و فرآوری | ارتباطات و رسانه | طراحی | زبان انگلیسی</t>
+          <t>هنرهای زیبا | آموزش و پرورش | مدیریت و اداره | تولید و فرآوری | ارتباطات و رسانه | طراحی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>هماهنگی حرکتی کل بدن | بیان شفاهی | ابتکار و اصالت | درک شفاهی | روانی و سیالی ایده‌ها | انعطاف‌پذیری حرکتی | تجسم فضایی</t>
+          <t>هماهنگی کلی بدن | بیان شفاهی | اصالت | درک شفاهی | روانی ایده‌ها | انعطاف‌پذیری دامنه حرکت | تجسم</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | استادان و مدرسان دانشگاهی هنر، تئاتر و موسیقی | رقصندگان | رهبران ارکستر، مدیران موسیقی و آهنگسازان | تهیه‌کنندگان و کارگردانان | معلمان دوره‌های آزاد و مهارت‌آموزی شخصی</t>
+          <t>بازیگران | مدیران هنری | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | هنرمندان رقص و حرکات موزون | رهبران ارکستر، مدیران موسیقی و آهنگسازان | تهیه‌کنندگان و کارگردانان | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | زبان انگلیسی | آموزش | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | فلسفه و الهیات</t>
+          <t>هنرهای زیبا | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتری و شخصی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت شنیداری | مرتب‌سازی اطلاعات | درک کتبی | روانی و سیالی ایده‌ها | ابتکار و اصالت | درک شفاهی | توجه شنوایی</t>
+          <t>حساسیت شنوایی | ترتیب‌دهی اطلاعات | درک کتبی | روانی ایده‌ها | اصالت | درک شفاهی | توجه شنیداری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>استادان و مدرسان دانشگاهی هنر، تئاتر و موسیقی | طراحان حرکت (کوروگراف‌ها) | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | موسیقی‌دانان و خوانندگان | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا</t>
+          <t>مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | طراحان حرکت و کوروگراف‌ها | موسیقی‌درمانگران | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | نوازندگان و خوانندگان | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
